--- a/final_data_pipeline/output/311513_elec_options.xlsx
+++ b/final_data_pipeline/output/311513_elec_options.xlsx
@@ -1844,7 +1844,7 @@
         <v>102</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1939,7 +1939,7 @@
         <v>102</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2037,7 +2037,7 @@
         <v>102</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2132,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2227,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2322,7 +2322,7 @@
         <v>102</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2417,7 +2417,7 @@
         <v>102</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2512,7 +2512,7 @@
         <v>102</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2607,7 +2607,7 @@
         <v>102</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2705,7 +2705,7 @@
         <v>102</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2800,7 +2800,7 @@
         <v>102</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2895,7 +2895,7 @@
         <v>102</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2990,7 +2990,7 @@
         <v>102</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -3085,7 +3085,7 @@
         <v>102</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3180,7 +3180,7 @@
         <v>102</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -3275,7 +3275,7 @@
         <v>102</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE27">
         <v>8000</v>
@@ -3373,7 +3373,7 @@
         <v>102</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE28">
         <v>8000</v>
@@ -3471,7 +3471,7 @@
         <v>102</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE29">
         <v>8000</v>
@@ -3569,7 +3569,7 @@
         <v>102</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE30">
         <v>8000</v>
@@ -3667,7 +3667,7 @@
         <v>102</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE31">
         <v>8000</v>
@@ -3765,7 +3765,7 @@
         <v>102</v>
       </c>
       <c r="AD32">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE32">
         <v>8000</v>
@@ -3863,7 +3863,7 @@
         <v>102</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE33">
         <v>8000</v>
@@ -3958,7 +3958,7 @@
         <v>102</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -4053,7 +4053,7 @@
         <v>102</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4148,7 +4148,7 @@
         <v>102</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4243,7 +4243,7 @@
         <v>102</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -4338,7 +4338,7 @@
         <v>102</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE38">
         <v>8000</v>
@@ -4433,7 +4433,7 @@
         <v>102</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE39">
         <v>8000</v>
@@ -4528,7 +4528,7 @@
         <v>102</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE40">
         <v>8000</v>
@@ -4623,7 +4623,7 @@
         <v>102</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE41">
         <v>8000</v>
@@ -4718,7 +4718,7 @@
         <v>102</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE42">
         <v>8000</v>
@@ -4813,7 +4813,7 @@
         <v>102</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE43">
         <v>8000</v>
@@ -4908,7 +4908,7 @@
         <v>102</v>
       </c>
       <c r="AD44">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE44">
         <v>8000</v>
@@ -5003,7 +5003,7 @@
         <v>102</v>
       </c>
       <c r="AD45">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE45">
         <v>8000</v>
@@ -5098,7 +5098,7 @@
         <v>102</v>
       </c>
       <c r="AD46">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE46">
         <v>8000</v>
@@ -5193,7 +5193,7 @@
         <v>102</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE47">
         <v>8000</v>
@@ -5288,7 +5288,7 @@
         <v>102</v>
       </c>
       <c r="AD48">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE48">
         <v>8000</v>
@@ -5383,7 +5383,7 @@
         <v>102</v>
       </c>
       <c r="AD49">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE49">
         <v>8000</v>
@@ -5481,7 +5481,7 @@
         <v>102</v>
       </c>
       <c r="AD50">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE50">
         <v>8000</v>
@@ -5576,7 +5576,7 @@
         <v>102</v>
       </c>
       <c r="AD51">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE51">
         <v>8000</v>
@@ -5674,7 +5674,7 @@
         <v>102</v>
       </c>
       <c r="AD52">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE52">
         <v>8000</v>
@@ -5769,7 +5769,7 @@
         <v>102</v>
       </c>
       <c r="AD53">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE53">
         <v>8000</v>
@@ -5864,7 +5864,7 @@
         <v>102</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -5959,7 +5959,7 @@
         <v>102</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6054,7 +6054,7 @@
         <v>102</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6149,7 +6149,7 @@
         <v>102</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6244,7 +6244,7 @@
         <v>102</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6339,7 +6339,7 @@
         <v>102</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6434,7 +6434,7 @@
         <v>102</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6529,7 +6529,7 @@
         <v>102</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6624,7 +6624,7 @@
         <v>102</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6719,7 +6719,7 @@
         <v>102</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6814,7 +6814,7 @@
         <v>102</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -6909,7 +6909,7 @@
         <v>102</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -7007,7 +7007,7 @@
         <v>102</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7105,7 +7105,7 @@
         <v>102</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -7200,7 +7200,7 @@
         <v>102</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -7295,7 +7295,7 @@
         <v>102</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -7390,7 +7390,7 @@
         <v>102</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7485,7 +7485,7 @@
         <v>102</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -8058,7 +8058,7 @@
         <v>102</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -8153,7 +8153,7 @@
         <v>102</v>
       </c>
       <c r="AD78">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE78">
         <v>8000</v>
@@ -8251,7 +8251,7 @@
         <v>102</v>
       </c>
       <c r="AD79">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE79">
         <v>8000</v>
@@ -8346,7 +8346,7 @@
         <v>102</v>
       </c>
       <c r="AD80">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE80">
         <v>8000</v>
@@ -8441,7 +8441,7 @@
         <v>102</v>
       </c>
       <c r="AD81">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE81">
         <v>8000</v>
@@ -11609,7 +11609,7 @@
         <v>102</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -11704,7 +11704,7 @@
         <v>102</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -11799,7 +11799,7 @@
         <v>102</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -11894,7 +11894,7 @@
         <v>102</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -11989,7 +11989,7 @@
         <v>102</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -12084,7 +12084,7 @@
         <v>102</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -12179,7 +12179,7 @@
         <v>102</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -12274,7 +12274,7 @@
         <v>102</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -12369,7 +12369,7 @@
         <v>102</v>
       </c>
       <c r="AD122">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE122">
         <v>8000</v>
@@ -12464,7 +12464,7 @@
         <v>102</v>
       </c>
       <c r="AD123">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE123">
         <v>8000</v>
@@ -12559,7 +12559,7 @@
         <v>102</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12654,7 +12654,7 @@
         <v>102</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12752,7 +12752,7 @@
         <v>102</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -12850,7 +12850,7 @@
         <v>102</v>
       </c>
       <c r="AD127">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE127">
         <v>8000</v>
@@ -12945,7 +12945,7 @@
         <v>102</v>
       </c>
       <c r="AD128">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE128">
         <v>8000</v>
@@ -13040,7 +13040,7 @@
         <v>102</v>
       </c>
       <c r="AD129">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE129">
         <v>8000</v>
@@ -13135,7 +13135,7 @@
         <v>102</v>
       </c>
       <c r="AD130">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE130">
         <v>8000</v>
@@ -13233,7 +13233,7 @@
         <v>102</v>
       </c>
       <c r="AD131">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE131">
         <v>8000</v>
@@ -13328,7 +13328,7 @@
         <v>102</v>
       </c>
       <c r="AD132">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE132">
         <v>8000</v>
@@ -13423,7 +13423,7 @@
         <v>102</v>
       </c>
       <c r="AD133">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE133">
         <v>8000</v>
@@ -13518,7 +13518,7 @@
         <v>102</v>
       </c>
       <c r="AD134">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE134">
         <v>8000</v>
@@ -13613,7 +13613,7 @@
         <v>102</v>
       </c>
       <c r="AD135">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE135">
         <v>8000</v>
@@ -13708,7 +13708,7 @@
         <v>102</v>
       </c>
       <c r="AD136">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE136">
         <v>8000</v>
@@ -13803,7 +13803,7 @@
         <v>102</v>
       </c>
       <c r="AD137">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE137">
         <v>8000</v>
@@ -13901,7 +13901,7 @@
         <v>102</v>
       </c>
       <c r="AD138">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE138">
         <v>8000</v>
@@ -13999,7 +13999,7 @@
         <v>102</v>
       </c>
       <c r="AD139">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE139">
         <v>8000</v>
@@ -14094,7 +14094,7 @@
         <v>102</v>
       </c>
       <c r="AD140">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE140">
         <v>8000</v>
@@ -14192,7 +14192,7 @@
         <v>102</v>
       </c>
       <c r="AD141">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE141">
         <v>8000</v>
@@ -14290,7 +14290,7 @@
         <v>102</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14385,7 +14385,7 @@
         <v>102</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -14480,7 +14480,7 @@
         <v>102</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -14575,7 +14575,7 @@
         <v>102</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -14670,7 +14670,7 @@
         <v>102</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -14768,7 +14768,7 @@
         <v>102</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -14866,7 +14866,7 @@
         <v>102</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -14961,7 +14961,7 @@
         <v>102</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -15056,7 +15056,7 @@
         <v>102</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -15151,7 +15151,7 @@
         <v>102</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -15246,7 +15246,7 @@
         <v>102</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -15341,7 +15341,7 @@
         <v>102</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -15436,7 +15436,7 @@
         <v>102</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE154">
         <v>8000</v>
@@ -15531,7 +15531,7 @@
         <v>102</v>
       </c>
       <c r="AD155">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE155">
         <v>8000</v>
@@ -15626,7 +15626,7 @@
         <v>102</v>
       </c>
       <c r="AD156">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE156">
         <v>8000</v>
@@ -15721,7 +15721,7 @@
         <v>102</v>
       </c>
       <c r="AD157">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE157">
         <v>8000</v>
@@ -15816,7 +15816,7 @@
         <v>102</v>
       </c>
       <c r="AD158">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE158">
         <v>8000</v>
@@ -15911,7 +15911,7 @@
         <v>102</v>
       </c>
       <c r="AD159">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE159">
         <v>8000</v>
@@ -16006,7 +16006,7 @@
         <v>102</v>
       </c>
       <c r="AD160">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE160">
         <v>8000</v>
@@ -16101,7 +16101,7 @@
         <v>102</v>
       </c>
       <c r="AD161">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE161">
         <v>8000</v>
@@ -16196,7 +16196,7 @@
         <v>102</v>
       </c>
       <c r="AD162">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE162">
         <v>8000</v>
@@ -16291,7 +16291,7 @@
         <v>102</v>
       </c>
       <c r="AD163">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE163">
         <v>8000</v>
@@ -16386,7 +16386,7 @@
         <v>102</v>
       </c>
       <c r="AD164">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE164">
         <v>8000</v>
@@ -16484,7 +16484,7 @@
         <v>102</v>
       </c>
       <c r="AD165">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE165">
         <v>8000</v>
@@ -16579,7 +16579,7 @@
         <v>102</v>
       </c>
       <c r="AD166">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE166">
         <v>8000</v>
@@ -16674,7 +16674,7 @@
         <v>102</v>
       </c>
       <c r="AD167">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE167">
         <v>8000</v>
@@ -16769,7 +16769,7 @@
         <v>102</v>
       </c>
       <c r="AD168">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE168">
         <v>8000</v>
@@ -16867,7 +16867,7 @@
         <v>102</v>
       </c>
       <c r="AD169">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE169">
         <v>8000</v>
@@ -16962,7 +16962,7 @@
         <v>102</v>
       </c>
       <c r="AD170">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE170">
         <v>8000</v>
@@ -17057,7 +17057,7 @@
         <v>102</v>
       </c>
       <c r="AD171">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE171">
         <v>8000</v>
@@ -17152,7 +17152,7 @@
         <v>102</v>
       </c>
       <c r="AD172">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE172">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>102</v>
       </c>
       <c r="AD173">
-        <v>10</v>
+        <v>-3.222222222222223</v>
       </c>
       <c r="AE173">
         <v>8000</v>
